--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484072_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484072_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8364</v>
+        <v>5.5902</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1061</v>
+        <v>6.9441</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2698</v>
+        <v>-1.3539</v>
       </c>
       <c r="G2" t="n">
         <v>5.6479</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.403</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4398</v>
+        <v>0.2778</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0368</v>
+        <v>-1.121</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6032</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>C. FONS TEIXIDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8084</v>
+        <v>2.6063</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2384</v>
+        <v>4.1542</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5701</v>
+        <v>-1.548</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8862</v>
+        <v>3.1023</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1865</v>
+        <v>1.8443</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0728</v>
+        <v>1.258</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7258</v>
+        <v>3.6372</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5995</v>
+        <v>2.4247</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3253</v>
+        <v>1.2125</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1604</v>
+        <v>-0.5349</v>
       </c>
       <c r="N3" t="n">
-        <v>0.413</v>
+        <v>-0.5804</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2526</v>
+        <v>0.0455</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>1.9838</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>2.9758</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4665</v>
+        <v>-2.1426</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4874</v>
+        <v>-0.5667</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0209</v>
+        <v>-1.5759</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. FONS TEIXIDO</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6869</v>
+        <v>2.469</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6838</v>
+        <v>0.6465</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9968</v>
+        <v>1.8226</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1023</v>
+        <v>0.8862</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8443</v>
+        <v>-0.1865</v>
       </c>
       <c r="I4" t="n">
-        <v>1.258</v>
+        <v>1.0728</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6372</v>
+        <v>0.7258</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4247</v>
+        <v>-0.5995</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2125</v>
+        <v>1.3253</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5349</v>
+        <v>0.1604</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5804</v>
+        <v>0.413</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0455</v>
+        <v>-0.2526</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9758</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.0619</v>
+        <v>0.1941</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0372</v>
+        <v>-0.0793</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.0248</v>
+        <v>0.2734</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4663</v>
+        <v>1.3082</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3644</v>
+        <v>-1.4664</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8307</v>
+        <v>2.7746</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2072</v>
@@ -844,13 +844,13 @@
         <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0488</v>
+        <v>-0.2069</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.255</v>
+        <v>-0.357</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2062</v>
+        <v>0.1501</v>
       </c>
       <c r="V5" t="n">
         <v>0.532</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1203</v>
+        <v>1.0096</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5507</v>
+        <v>1.4161</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4303</v>
+        <v>-0.4065</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3819</v>
+        <v>2.3054</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6902</v>
+        <v>-0.8105</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3083</v>
+        <v>3.1159</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4231</v>
+        <v>2.0403</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3427</v>
+        <v>-1.1726</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0803</v>
+        <v>3.2129</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0412</v>
+        <v>0.265</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3474</v>
+        <v>0.3621</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3886</v>
+        <v>-0.097</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5952</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7465000000000001</v>
+        <v>-1.6169</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8616</v>
+        <v>-0.8388</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1151</v>
+        <v>-0.7781</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6032</v>
+        <v>-0.8692</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8692</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.854</v>
+        <v>0.6586</v>
       </c>
       <c r="E7" t="n">
-        <v>1.008</v>
+        <v>0.8365</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.154</v>
+        <v>-0.1778</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3054</v>
+        <v>0.3819</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8105</v>
+        <v>0.6902</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1159</v>
+        <v>-0.3083</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0403</v>
+        <v>0.4231</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1726</v>
+        <v>0.3427</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2129</v>
+        <v>0.0803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.265</v>
+        <v>-0.0412</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3621</v>
+        <v>0.3474</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.097</v>
+        <v>-0.3886</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1822</v>
+        <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7725</v>
+        <v>0.2848</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2469</v>
+        <v>0.1474</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5256</v>
+        <v>0.1374</v>
       </c>
       <c r="V7" t="n">
+        <v>-0.6032</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X7" t="n">
         <v>-0.8692</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.2065</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-2.0757</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
+        <v>-0.8241000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="F8" t="n">
         <v>-0.8839</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.3086</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.5753</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8608</v>
@@ -1078,13 +1078,13 @@
         <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0606</v>
+        <v>0.1204</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.289</v>
+        <v>0.0794</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3496</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4724</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.92</v>
+        <v>-2.2963</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7183</v>
+        <v>-3.758</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7983</v>
+        <v>1.4617</v>
       </c>
       <c r="G9" t="n">
         <v>1.8711</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3039</v>
+        <v>-0.6802</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1418</v>
+        <v>0.1021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4457</v>
+        <v>-0.7823</v>
       </c>
       <c r="V9" t="n">
         <v>1.4724</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9762</v>
+        <v>-2.5579</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3285</v>
+        <v>-3.0224</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3523</v>
+        <v>0.4645</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1639</v>
@@ -1234,13 +1234,13 @@
         <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5382</v>
+        <v>-2.1199</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9862</v>
+        <v>-0.6801</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5521</v>
+        <v>-1.4398</v>
       </c>
       <c r="V10" t="n">
         <v>0.3373</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9946</v>
+        <v>-2.6543</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2372</v>
+        <v>-2.8688</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2426</v>
+        <v>0.2145</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0961</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1807</v>
+        <v>-0.8403</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0599</v>
+        <v>-0.6914</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1208</v>
+        <v>-0.1489</v>
       </c>
       <c r="V11" t="n">
         <v>0.8692</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.997599999999998</v>
+        <v>5.309300000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.629999999999999</v>
+        <v>2.941599999999999</v>
       </c>
       <c r="F12" t="n">
         <v>2.3678</v>
@@ -1381,7 +1381,7 @@
         <v>-1.7155</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9677</v>
+        <v>3.967699999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.8868</v>
@@ -1390,13 +1390,13 @@
         <v>17.8546</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.1624</v>
+        <v>-7.850699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.9184</v>
+        <v>-2.6066</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.2442</v>
+        <v>-5.2441</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6743999999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1031</v>
+        <v>4.1751</v>
       </c>
       <c r="E13" t="n">
-        <v>6.988</v>
+        <v>1.9888</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1151</v>
+        <v>2.1863</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6252</v>
+        <v>-0.1972</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0433</v>
+        <v>1.6632</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5819</v>
+        <v>-1.8604</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4662</v>
+        <v>1.5458</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4958</v>
+        <v>1.4176</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9705</v>
+        <v>0.1281</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8411</v>
+        <v>-1.743</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4525</v>
+        <v>0.2456</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3886</v>
+        <v>-1.9886</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.3725</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.9596</v>
+        <v>-2.9758</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5871</v>
+        <v>2.7774</v>
       </c>
       <c r="S13" t="n">
-        <v>7.8505</v>
+        <v>1.5545</v>
       </c>
       <c r="T13" t="n">
-        <v>6.2749</v>
+        <v>0.4026</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5756</v>
+        <v>1.1519</v>
       </c>
       <c r="V13" t="n">
+        <v>3.0162</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.0162</v>
+      </c>
+      <c r="X13" t="n">
         <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.2065</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.2065</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6503</v>
+        <v>3.3238</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0908</v>
+        <v>3.047</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5595</v>
+        <v>0.2768</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1972</v>
+        <v>0.5548</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6632</v>
+        <v>-1.4518</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8604</v>
+        <v>2.0067</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5458</v>
+        <v>3.3813</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4176</v>
+        <v>-0.8861</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1281</v>
+        <v>4.2673</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.743</v>
+        <v>-2.8264</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2456</v>
+        <v>-0.5658</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9886</v>
+        <v>-2.2607</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7774</v>
+        <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0297</v>
+        <v>1.1819</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5047</v>
+        <v>0.6577</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5251</v>
+        <v>0.5242</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0162</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0162</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3325</v>
+        <v>3.3111</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7206</v>
+        <v>3.621</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3881</v>
+        <v>-0.31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5548</v>
+        <v>2.6252</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4518</v>
+        <v>1.0433</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0067</v>
+        <v>1.5819</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3813</v>
+        <v>4.4662</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8861</v>
+        <v>2.4958</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2673</v>
+        <v>1.9705</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8264</v>
+        <v>-1.8411</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5658</v>
+        <v>-1.4525</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2607</v>
+        <v>-0.3886</v>
       </c>
       <c r="P15" t="n">
+        <v>-3.3725</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-4.9596</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.5871</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.9919</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.579</v>
-      </c>
       <c r="S15" t="n">
-        <v>-0.8094</v>
+        <v>4.0584</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6687</v>
+        <v>2.9079</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1407</v>
+        <v>1.1505</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2983</v>
+        <v>0.5407</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8003</v>
+        <v>0.9023</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.502</v>
+        <v>-0.3617</v>
       </c>
       <c r="G16" t="n">
         <v>1.5137</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3542</v>
+        <v>-0.1119</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1757</v>
+        <v>-0.0737</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1786</v>
+        <v>-0.0383</v>
       </c>
       <c r="V16" t="n">
         <v>-0.266</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3856</v>
+        <v>-2.2597</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3589</v>
+        <v>-0.7634</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7445</v>
+        <v>-1.4963</v>
       </c>
       <c r="G17" t="n">
         <v>-2.3957</v>
@@ -1780,13 +1780,13 @@
         <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2085</v>
+        <v>0.3345</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4795</v>
+        <v>0.3572</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.271</v>
+        <v>-0.0227</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.227</v>
+        <v>-3.3907</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1092</v>
+        <v>-1.3835</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1177</v>
+        <v>-2.0072</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.2633</v>
+        <v>-2.9542</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9376</v>
+        <v>0.6541</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3257</v>
+        <v>-3.6083</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.7024</v>
+        <v>0.1443</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6293</v>
+        <v>1.492</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.0731</v>
+        <v>-1.3476</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5609</v>
+        <v>-3.0985</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3083</v>
+        <v>-0.8378</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2526</v>
+        <v>-2.2607</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,28 +1858,28 @@
         <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.42</v>
+        <v>1.0359</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2209</v>
+        <v>0.5273</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.199</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5437</v>
+        <v>-1.4724</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.0713</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3417</v>
+        <v>-1.4012</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.2876</v>
+        <v>-4.114</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8119</v>
+        <v>-3.497</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4757</v>
+        <v>-0.617</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9542</v>
+        <v>-3.2633</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6541</v>
+        <v>-0.9376</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.6083</v>
+        <v>-2.3257</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1443</v>
+        <v>-2.7024</v>
       </c>
       <c r="K19" t="n">
-        <v>1.492</v>
+        <v>-0.6293</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3476</v>
+        <v>-2.0731</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0985</v>
+        <v>-0.5609</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8378</v>
+        <v>-0.3083</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2607</v>
+        <v>-0.2526</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1936,22 +1936,22 @@
         <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.861</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9011</v>
+        <v>0.3912</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0401</v>
+        <v>0.3017</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4724</v>
+        <v>-1.5437</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0713</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4012</v>
+        <v>-2.3417</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.4817</v>
+        <v>-5.2234</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.4054</v>
+        <v>-6.2831</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9237</v>
+        <v>1.0597</v>
       </c>
       <c r="G20" t="n">
         <v>-5.7501</v>
@@ -2014,13 +2014,13 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4818</v>
+        <v>0.7765</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0485</v>
+        <v>0.0738</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5667</v>
+        <v>0.7027</v>
       </c>
       <c r="V20" t="n">
         <v>0.9405</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.997700000000002</v>
+        <v>-3.637099999999998</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.367899999999999</v>
+        <v>-2.367900000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.629699999999999</v>
+        <v>-1.269399999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-9.866800000000001</v>
@@ -2065,7 +2065,7 @@
         <v>-8.2273</v>
       </c>
       <c r="J21" t="n">
-        <v>2.880400000000002</v>
+        <v>2.8804</v>
       </c>
       <c r="K21" t="n">
         <v>1.1649</v>
@@ -2092,13 +2092,13 @@
         <v>13.8869</v>
       </c>
       <c r="S21" t="n">
-        <v>8.1623</v>
+        <v>9.5228</v>
       </c>
       <c r="T21" t="n">
-        <v>5.244199999999999</v>
+        <v>5.244</v>
       </c>
       <c r="U21" t="n">
-        <v>2.9182</v>
+        <v>4.2786</v>
       </c>
       <c r="V21" t="n">
         <v>0.6745999999999999</v>
